--- a/src/utils/sxsyzlzq/friends/xingkong/zz_xk_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/xingkong/zz_xk_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13395" activeTab="6"/>
+    <workbookView windowWidth="16515" windowHeight="10335" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="萨维丽娅" sheetId="1" r:id="rId1"/>
@@ -173,7 +173,7 @@
     <t>学仆-观测型</t>
   </si>
   <si>
-    <t>沉默否定</t>
+    <t>沉重否定</t>
   </si>
   <si>
     <t>破魔系教授</t>
@@ -2757,7 +2757,7 @@
         <v>5</v>
       </c>
       <c r="D39" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2810,7 +2810,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>15.5714285714286</v>
+        <v>15.7142857142857</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2821,7 +2821,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D11,D17:D29,D35:D41)</f>
-        <v>16.2</v>
+        <v>16.2333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -3296,7 +3296,7 @@
         <v>5</v>
       </c>
       <c r="D39" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3349,7 +3349,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>15.5714285714286</v>
+        <v>15.7142857142857</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3360,7 +3360,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D9,D15:D29,D35:D41)</f>
-        <v>15.1666666666667</v>
+        <v>15.2</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/friends/xingkong/zz_xk_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/xingkong/zz_xk_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16515" windowHeight="10335" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="13395"/>
   </bookViews>
   <sheets>
     <sheet name="萨维丽娅" sheetId="1" r:id="rId1"/>
@@ -1458,7 +1458,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1542,7 +1542,7 @@
         <v>4</v>
       </c>
       <c r="D26" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1611,7 +1611,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D19:D29)</f>
-        <v>16.7272727272727</v>
+        <v>16.9090909090909</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1745,7 +1745,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D13,D19:D29,D35:D41)</f>
-        <v>16.9</v>
+        <v>16.9666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2507,7 +2507,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2591,7 +2591,7 @@
         <v>4</v>
       </c>
       <c r="D24" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2687,7 +2687,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D17:D29)</f>
-        <v>15.6923076923077</v>
+        <v>15.8461538461538</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2821,7 +2821,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D11,D17:D29,D35:D41)</f>
-        <v>16.2333333333333</v>
+        <v>16.3</v>
       </c>
     </row>
   </sheetData>
@@ -3101,7 +3101,7 @@
         <v>4</v>
       </c>
       <c r="D22" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3226,7 +3226,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D15:D29)</f>
-        <v>14.3333333333333</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3360,7 +3360,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D9,D15:D29,D35:D41)</f>
-        <v>15.2</v>
+        <v>15.2333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -3510,7 +3510,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -3554,7 +3554,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C24" s="2">
         <f>AVERAGE(C14:C21)</f>
-        <v>17</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C38" s="4">
         <f>AVERAGE(C2:C8,C14:C21,C27:C32)</f>
-        <v>17.3333333333333</v>
+        <v>17.4285714285714</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/friends/xingkong/zz_xk_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/xingkong/zz_xk_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13395"/>
+    <workbookView windowWidth="27945" windowHeight="13395" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="萨维丽娅" sheetId="1" r:id="rId1"/>
@@ -1307,7 +1307,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1430,7 +1430,7 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1">
         <f>AVERAGE(D2:D13)</f>
-        <v>17.6666666666667</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1745,7 +1745,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D13,D19:D29,D35:D41)</f>
-        <v>16.9666666666667</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1846,7 +1846,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1997,7 +1997,7 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1">
         <f>AVERAGE(D2:D15)</f>
-        <v>16.4285714285714</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2283,7 +2283,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D15,D21:D28,D34:D41)</f>
-        <v>16.2666666666667</v>
+        <v>16.3</v>
       </c>
     </row>
   </sheetData>
@@ -2535,7 +2535,7 @@
         <v>2</v>
       </c>
       <c r="D20" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2687,7 +2687,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D17:D29)</f>
-        <v>15.8461538461538</v>
+        <v>15.9230769230769</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2821,7 +2821,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D11,D17:D29,D35:D41)</f>
-        <v>16.3</v>
+        <v>16.3333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -3017,7 +3017,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -3226,7 +3226,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D15:D29)</f>
-        <v>14.4</v>
+        <v>14.4666666666667</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3360,7 +3360,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D9,D15:D29,D35:D41)</f>
-        <v>15.2333333333333</v>
+        <v>15.2666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -3770,7 +3770,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="C13" s="1">
         <f>AVERAGE(C2:C10)</f>
-        <v>15.2222222222222</v>
+        <v>15.3333333333333</v>
       </c>
       <c r="D13" s="2"/>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C10,C16:C19,C25:C26)</f>
-        <v>15</v>
+        <v>15.0666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -4076,7 +4076,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C11:C20)</f>
-        <v>12.9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C5,C11:C20,C26:C26)</f>
-        <v>13.2666666666667</v>
+        <v>13.3333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/friends/xingkong/zz_xk_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/xingkong/zz_xk_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13395" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="13395" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="萨维丽娅" sheetId="1" r:id="rId1"/>
@@ -1570,7 +1570,7 @@
         <v>5</v>
       </c>
       <c r="D28" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F28" s="5"/>
     </row>
@@ -1611,7 +1611,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D19:D29)</f>
-        <v>16.9090909090909</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1745,7 +1745,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D13,D19:D29,D35:D41)</f>
-        <v>17</v>
+        <v>17.0333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2095,7 +2095,7 @@
         <v>5</v>
       </c>
       <c r="D27" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2135,7 +2135,7 @@
       <c r="C31" s="2"/>
       <c r="D31" s="2">
         <f>AVERAGE(D21:D28)</f>
-        <v>16.75</v>
+        <v>16.875</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2283,7 +2283,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D15,D21:D28,D34:D41)</f>
-        <v>16.3</v>
+        <v>16.3333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2619,7 +2619,7 @@
         <v>5</v>
       </c>
       <c r="D26" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2687,7 +2687,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D17:D29)</f>
-        <v>15.9230769230769</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2821,7 +2821,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D11,D17:D29,D35:D41)</f>
-        <v>16.3333333333333</v>
+        <v>16.3666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -3087,7 +3087,7 @@
         <v>3</v>
       </c>
       <c r="D21" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -3157,7 +3157,7 @@
         <v>5</v>
       </c>
       <c r="D26" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -3226,7 +3226,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D15:D29)</f>
-        <v>14.4666666666667</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3360,7 +3360,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D9,D15:D29,D35:D41)</f>
-        <v>15.2666666666667</v>
+        <v>15.3333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -3565,7 +3565,7 @@
         <v>5</v>
       </c>
       <c r="C20" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C24" s="2">
         <f>AVERAGE(C14:C21)</f>
-        <v>17.25</v>
+        <v>17.375</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C38" s="4">
         <f>AVERAGE(C2:C8,C14:C21,C27:C32)</f>
-        <v>17.4285714285714</v>
+        <v>17.4761904761905</v>
       </c>
     </row>
   </sheetData>
@@ -4120,7 +4120,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C11:C20)</f>
-        <v>13</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C5,C11:C20,C26:C26)</f>
-        <v>13.3333333333333</v>
+        <v>13.4</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/friends/xingkong/zz_xk_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/xingkong/zz_xk_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13395" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="13395"/>
   </bookViews>
   <sheets>
     <sheet name="萨维丽娅" sheetId="1" r:id="rId1"/>
@@ -158,10 +158,10 @@
     <t>魔力风暴</t>
   </si>
   <si>
-    <t>黑旗舰队水手</t>
-  </si>
-  <si>
     <t>黑旗舰队飞斧手</t>
+  </si>
+  <si>
+    <t>海神赐福</t>
   </si>
   <si>
     <t>烈日大祭师</t>
@@ -1444,7 +1444,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1611,7 +1611,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D19:D29)</f>
-        <v>17</v>
+        <v>17.0909090909091</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1745,7 +1745,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D13,D19:D29,D35:D41)</f>
-        <v>17.0333333333333</v>
+        <v>17.0666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1927,7 +1927,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="1">
         <v>15</v>
@@ -1935,16 +1935,16 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1962,18 +1962,10 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="1">
-        <v>5</v>
-      </c>
-      <c r="D15" s="1">
-        <v>17</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1"/>
@@ -1982,27 +1974,35 @@
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1">
-        <f>AVERAGE(D2:D15)</f>
-        <v>16.5</v>
+      <c r="D17" s="1">
+        <f>AVERAGE(D2:D14)</f>
+        <v>16.6153846153846</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>18</v>
@@ -2011,12 +2011,12 @@
         <v>2</v>
       </c>
       <c r="D21" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>18</v>
@@ -2025,7 +2025,7 @@
         <v>2</v>
       </c>
       <c r="D22" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2134,8 +2134,8 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2">
-        <f>AVERAGE(D21:D28)</f>
-        <v>16.875</v>
+        <f>AVERAGE(D20:D28)</f>
+        <v>16.2222222222222</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2149,7 +2149,7 @@
         <v>2</v>
       </c>
       <c r="D34" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2272,7 +2272,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D34:D41)</f>
-        <v>15.5</v>
+        <v>15.625</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2282,8 +2282,8 @@
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4">
-        <f>AVERAGE(D2:D15,D21:D28,D34:D41)</f>
-        <v>16.3333333333333</v>
+        <f>AVERAGE(D2:D14,D20:D28,D34:D41)</f>
+        <v>16.2333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2493,7 +2493,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2687,7 +2687,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D17:D29)</f>
-        <v>16</v>
+        <v>16.0769230769231</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2821,7 +2821,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D11,D17:D29,D35:D41)</f>
-        <v>16.3666666666667</v>
+        <v>16.4</v>
       </c>
     </row>
   </sheetData>
@@ -3499,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C24" s="2">
         <f>AVERAGE(C14:C21)</f>
-        <v>17.375</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C38" s="4">
         <f>AVERAGE(C2:C8,C14:C21,C27:C32)</f>
-        <v>17.4761904761905</v>
+        <v>17.5238095238095</v>
       </c>
     </row>
   </sheetData>
@@ -3811,55 +3811,55 @@
         <v>41</v>
       </c>
       <c r="B9" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="1">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1">
-        <v>15</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="1">
-        <f>AVERAGE(C2:C10)</f>
-        <v>15.3333333333333</v>
-      </c>
-      <c r="D13" s="2"/>
+      <c r="C12" s="1">
+        <f>AVERAGE(C2:C9)</f>
+        <v>15.375</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>18</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
       </c>
       <c r="C16" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3913,8 +3913,8 @@
         <v>29</v>
       </c>
       <c r="C22" s="2">
-        <f>AVERAGE(C16:C19)</f>
-        <v>15.25</v>
+        <f>AVERAGE(C15:C19)</f>
+        <v>14.4</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3925,7 +3925,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C25:C26)</f>
-        <v>13.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -3969,8 +3969,8 @@
         <v>68</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C10,C16:C19,C25:C26)</f>
-        <v>15.0666666666667</v>
+        <f>AVERAGE(C2:C9,C15:C19,C25:C26)</f>
+        <v>14.8666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/friends/xingkong/zz_xk_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/xingkong/zz_xk_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13395"/>
+    <workbookView windowWidth="17625" windowHeight="10680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="萨维丽娅" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="71">
   <si>
     <t>名称</t>
   </si>
@@ -1251,7 +1251,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1307,7 +1307,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1430,7 +1430,7 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1">
         <f>AVERAGE(D2:D13)</f>
-        <v>17.75</v>
+        <v>17.9166666666667</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1500,7 +1500,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1514,7 +1514,7 @@
         <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1528,7 +1528,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1611,7 +1611,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D19:D29)</f>
-        <v>17.0909090909091</v>
+        <v>17.3636363636364</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1653,7 +1653,7 @@
         <v>4</v>
       </c>
       <c r="D37" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1681,7 +1681,7 @@
         <v>5</v>
       </c>
       <c r="D39" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1695,7 +1695,7 @@
         <v>6</v>
       </c>
       <c r="D40" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1734,7 +1734,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>15.8571428571429</v>
+        <v>16.2857142857143</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1745,7 +1745,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D13,D19:D29,D35:D41)</f>
-        <v>17.0666666666667</v>
+        <v>17.3333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1790,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1846,7 +1846,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1916,7 +1916,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1930,7 +1930,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1983,26 +1983,26 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1">
         <f>AVERAGE(D2:D14)</f>
-        <v>16.6153846153846</v>
+        <v>16.9230769230769</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>18</v>
@@ -2011,12 +2011,12 @@
         <v>2</v>
       </c>
       <c r="D21" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>18</v>
@@ -2025,26 +2025,26 @@
         <v>2</v>
       </c>
       <c r="D22" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C23" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>18</v>
@@ -2053,26 +2053,26 @@
         <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C25" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>18</v>
@@ -2081,21 +2081,21 @@
         <v>4</v>
       </c>
       <c r="D26" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2135,7 +2135,7 @@
       <c r="C31" s="2"/>
       <c r="D31" s="2">
         <f>AVERAGE(D20:D28)</f>
-        <v>16.2222222222222</v>
+        <v>16.5555555555556</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2191,7 +2191,7 @@
         <v>4</v>
       </c>
       <c r="D37" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2219,7 +2219,7 @@
         <v>5</v>
       </c>
       <c r="D39" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2233,7 +2233,7 @@
         <v>6</v>
       </c>
       <c r="D40" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2272,7 +2272,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D34:D41)</f>
-        <v>15.625</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2283,7 +2283,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D14,D20:D28,D34:D41)</f>
-        <v>16.2333333333333</v>
+        <v>16.5666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2328,7 +2328,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2479,7 +2479,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1">
         <f>AVERAGE(D2:D11)</f>
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2549,7 +2549,7 @@
         <v>3</v>
       </c>
       <c r="D21" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2563,7 +2563,7 @@
         <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2687,7 +2687,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D17:D29)</f>
-        <v>16.0769230769231</v>
+        <v>16.2307692307692</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2729,7 +2729,7 @@
         <v>4</v>
       </c>
       <c r="D37" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2771,7 +2771,7 @@
         <v>6</v>
       </c>
       <c r="D40" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2810,7 +2810,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>15.7142857142857</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2821,7 +2821,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D11,D17:D29,D35:D41)</f>
-        <v>16.4</v>
+        <v>16.5666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2866,7 +2866,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2989,7 +2989,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <f>AVERAGE(D2:D9)</f>
-        <v>16.375</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3045,7 +3045,7 @@
         <v>3</v>
       </c>
       <c r="D18" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -3073,7 +3073,7 @@
         <v>3</v>
       </c>
       <c r="D20" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -3129,7 +3129,7 @@
         <v>4</v>
       </c>
       <c r="D24" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -3226,7 +3226,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2">
         <f>AVERAGE(D15:D29)</f>
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3268,7 +3268,7 @@
         <v>4</v>
       </c>
       <c r="D37" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3310,7 +3310,7 @@
         <v>6</v>
       </c>
       <c r="D40" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3349,7 +3349,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3">
         <f>AVERAGE(D35:D41)</f>
-        <v>15.7142857142857</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3360,7 +3360,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4">
         <f>AVERAGE(D2:D9,D15:D29,D35:D41)</f>
-        <v>15.3333333333333</v>
+        <v>15.5333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -3387,8 +3387,8 @@
       <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
-        <v>3</v>
+      <c r="C1">
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3399,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C11" s="1">
         <f>AVERAGE(C2:C8)</f>
-        <v>18.7142857142857</v>
+        <v>18.8571428571429</v>
       </c>
       <c r="D11" s="2"/>
     </row>
@@ -3532,7 +3532,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3543,7 +3543,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C24" s="2">
         <f>AVERAGE(C14:C21)</f>
-        <v>17.5</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3631,7 +3631,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -3653,7 +3653,7 @@
         <v>6</v>
       </c>
       <c r="C31" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="C35" s="3">
         <f>AVERAGE(C27:C32)</f>
-        <v>16.1666666666667</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -3698,12 +3698,15 @@
       </c>
       <c r="C38" s="4">
         <f>AVERAGE(C2:C8,C14:C21,C27:C32)</f>
-        <v>17.5238095238095</v>
+        <v>17.7619047619048</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="C38 C11" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -3770,7 +3773,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3803,7 +3806,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3814,7 +3817,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3836,7 +3839,7 @@
       </c>
       <c r="C12" s="1">
         <f>AVERAGE(C2:C9)</f>
-        <v>15.375</v>
+        <v>15.75</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -3859,7 +3862,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -3870,7 +3873,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3914,7 +3917,7 @@
       </c>
       <c r="C22" s="2">
         <f>AVERAGE(C15:C19)</f>
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3936,7 +3939,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3958,7 +3961,7 @@
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C25:C26)</f>
-        <v>14</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -3970,7 +3973,7 @@
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C9,C15:C19,C25:C26)</f>
-        <v>14.8666666666667</v>
+        <v>15.2666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -4109,7 +4112,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4142,7 +4145,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4197,7 +4200,7 @@
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C11:C20)</f>
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4242,7 +4245,7 @@
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C5,C11:C20,C26:C26)</f>
-        <v>13.4</v>
+        <v>13.5333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/friends/xingkong/zz_xk_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/xingkong/zz_xk_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12555" windowHeight="11160" activeTab="4"/>
+    <workbookView windowWidth="13980" windowHeight="11415"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
@@ -1334,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1345,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1400,7 +1400,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="C21" s="2">
         <f>AVERAGE(C12:C18)</f>
-        <v>20.8571428571429</v>
+        <v>21.2857142857143</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1433,7 +1433,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1488,7 +1488,7 @@
         <v>8</v>
       </c>
       <c r="C29" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C24:C29)</f>
-        <v>20.1666666666667</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1522,14 +1522,14 @@
       </c>
       <c r="C35" s="5">
         <f>AVERAGE(C2:C6,C12:C18,C24:C29)</f>
-        <v>20.7222222222222</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C9 C35" formulaRange="1"/>
+    <ignoredError sqref="C35 C9" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1608,7 +1608,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C12" s="1">
         <f>AVERAGE(C2:C9)</f>
-        <v>19</v>
+        <v>19.125</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -1752,7 +1752,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="C29" s="4">
         <f>AVERAGE(C23:C26)</f>
-        <v>17.5</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C9,C15:C17,C23:C26)</f>
-        <v>18.6666666666667</v>
+        <v>18.8</v>
       </c>
     </row>
   </sheetData>
@@ -1925,7 +1925,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1980,7 +1980,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C13:C20)</f>
-        <v>15.875</v>
+        <v>16.125</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C32" s="5">
         <f>AVERAGE(C2:C7,C13:C20,C26:C26)</f>
-        <v>16.2</v>
+        <v>16.3333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2523,7 +2523,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2594,24 +2594,24 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B25" s="2">
         <v>4</v>
       </c>
       <c r="C25" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B26" s="2">
         <v>4</v>
       </c>
       <c r="C26" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E26" s="3"/>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="C29" s="2">
         <f>AVERAGE(C18:C26)</f>
-        <v>20.5555555555556</v>
+        <v>20.8888888888889</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2656,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="C33" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2700,7 +2700,7 @@
         <v>4</v>
       </c>
       <c r="C37" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2744,7 +2744,7 @@
         <v>8</v>
       </c>
       <c r="C41" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="C44" s="4">
         <f>AVERAGE(C32:C41)</f>
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="C47" s="5">
         <f>AVERAGE(C2:C12,C18:C26,C32:C41)</f>
-        <v>20.0666666666667</v>
+        <v>20.2666666666667</v>
       </c>
     </row>
   </sheetData>
